--- a/完整需求开发配置表.xlsx
+++ b/完整需求开发配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13440" activeTab="3"/>
+    <workbookView windowWidth="29100" windowHeight="13380" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="猫咪基础配置表" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="258">
   <si>
     <t>猫咪ID</t>
   </si>
@@ -43,10 +43,16 @@
     <t>稀有度</t>
   </si>
   <si>
-    <t>主动技能</t>
-  </si>
-  <si>
-    <t>专属被动</t>
+    <t>主动技能名称</t>
+  </si>
+  <si>
+    <t>主动技能描述</t>
+  </si>
+  <si>
+    <t>专属被动技能名称</t>
+  </si>
+  <si>
+    <t>专属被动技能描述</t>
   </si>
   <si>
     <t>分配性格</t>
@@ -58,259 +64,382 @@
     <t>cat_001</t>
   </si>
   <si>
+    <t>橘猫</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>挑出来</t>
+  </si>
+  <si>
+    <t>将收集槽中最底层2张牌移动到临时存放槽中</t>
+  </si>
+  <si>
+    <t>吃得多</t>
+  </si>
+  <si>
+    <t>每局计时从开局2秒后开始计算</t>
+  </si>
+  <si>
+    <t>10种默认性格随机一种</t>
+  </si>
+  <si>
+    <t>陌生</t>
+  </si>
+  <si>
+    <t>cat_002</t>
+  </si>
+  <si>
+    <t>黑猫</t>
+  </si>
+  <si>
+    <t>撤回</t>
+  </si>
+  <si>
+    <t>撤销上一步操作</t>
+  </si>
+  <si>
+    <t>灵光</t>
+  </si>
+  <si>
+    <t>临时存放层槽位上限+1格</t>
+  </si>
+  <si>
+    <t>cat_003</t>
+  </si>
+  <si>
+    <t>白猫</t>
+  </si>
+  <si>
+    <t>重整</t>
+  </si>
+  <si>
+    <t>重新打乱当前所有可点击卡牌</t>
+  </si>
+  <si>
+    <t>醒目</t>
+  </si>
+  <si>
+    <t>每局开局立即消除1组可消除组合</t>
+  </si>
+  <si>
+    <t>cat_004</t>
+  </si>
+  <si>
     <t>蓝猫</t>
   </si>
   <si>
-    <t>N级（普通）</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>基础鱼干收益+10%</t>
+    <t>冻结</t>
+  </si>
+  <si>
+    <t>5秒内计时暂停</t>
+  </si>
+  <si>
+    <t>沉静</t>
+  </si>
+  <si>
+    <t>鱼干+10%</t>
+  </si>
+  <si>
+    <t>cat_005</t>
+  </si>
+  <si>
+    <t>布偶猫</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>叼走</t>
+  </si>
+  <si>
+    <t>将收集槽中最底层3张牌移动到临时存放槽中</t>
+  </si>
+  <si>
+    <t>贵宾</t>
+  </si>
+  <si>
+    <t>鱼干+20%</t>
+  </si>
+  <si>
+    <t>cat_006</t>
+  </si>
+  <si>
+    <t>三花猫</t>
+  </si>
+  <si>
+    <t>蹦跶</t>
+  </si>
+  <si>
+    <t>随机跳走2张干扰卡</t>
+  </si>
+  <si>
+    <t>收获</t>
+  </si>
+  <si>
+    <t>临时存放层槽位上限+2格</t>
+  </si>
+  <si>
+    <t>cat_007</t>
+  </si>
+  <si>
+    <t>暹罗猫</t>
+  </si>
+  <si>
+    <t>瞬移</t>
+  </si>
+  <si>
+    <t>将收集槽3张卡打乱放回棋盘</t>
+  </si>
+  <si>
+    <t>吃得快</t>
+  </si>
+  <si>
+    <t>每局计时从开局5秒后开始计算</t>
+  </si>
+  <si>
+    <t>cat_008</t>
+  </si>
+  <si>
+    <t>无毛猫</t>
+  </si>
+  <si>
+    <t>灼烧</t>
+  </si>
+  <si>
+    <t>清除最顶层3张卡牌</t>
+  </si>
+  <si>
+    <t>爪痕</t>
+  </si>
+  <si>
+    <t>每局自动移出1张干扰卡</t>
+  </si>
+  <si>
+    <t>cat_009</t>
+  </si>
+  <si>
+    <t>波斯猫</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>吐息</t>
+  </si>
+  <si>
+    <t>将收集槽中卡牌填满目前临时存放槽</t>
+  </si>
+  <si>
+    <t>优雅步调</t>
+  </si>
+  <si>
+    <t>每局额外1次重来机会</t>
+  </si>
+  <si>
+    <t>cat_010</t>
+  </si>
+  <si>
+    <t>折耳猫</t>
+  </si>
+  <si>
+    <t>听声</t>
+  </si>
+  <si>
+    <t>撤销前2步 ，同时不计入失败次数</t>
+  </si>
+  <si>
+    <t>猫之眼</t>
+  </si>
+  <si>
+    <t>被遮挡的卡牌仍以半透明显示</t>
+  </si>
+  <si>
+    <t>cat_011</t>
+  </si>
+  <si>
+    <t>星空猫</t>
+  </si>
+  <si>
+    <t>SSR</t>
+  </si>
+  <si>
+    <t>永昼</t>
+  </si>
+  <si>
+    <t>有一定几率，直接跳过本关</t>
+  </si>
+  <si>
+    <t>观星</t>
+  </si>
+  <si>
+    <t>猫咪喜欢观星，并在游戏中时刻祝福你</t>
+  </si>
+  <si>
+    <t>cat_012</t>
+  </si>
+  <si>
+    <t>幸运猫</t>
+  </si>
+  <si>
+    <t>洗牌</t>
+  </si>
+  <si>
+    <t>重新打乱当前棋盘所有卡牌</t>
+  </si>
+  <si>
+    <t>福星</t>
+  </si>
+  <si>
+    <t>鱼干+40%</t>
+  </si>
+  <si>
+    <t>注意：</t>
+  </si>
+  <si>
+    <t>每只猫咪只有一种性格，性格分配从“黏人，吃货，胆小，傲娇，胆大，高冷，话痨，懒散，独行，狡黠”中随机产生</t>
+  </si>
+  <si>
+    <t>分类</t>
+  </si>
+  <si>
+    <t>性格ID</t>
+  </si>
+  <si>
+    <t>性格名称</t>
+  </si>
+  <si>
+    <t>核心效果</t>
+  </si>
+  <si>
+    <t>玩法说明</t>
+  </si>
+  <si>
+    <t>技能循环类</t>
+  </si>
+  <si>
+    <t>char_001</t>
+  </si>
+  <si>
+    <t>傲娇</t>
+  </si>
+  <si>
+    <t>主动技能冷却缩减，高好感度下额外增加1次本局技能使用次数</t>
+  </si>
+  <si>
+    <t>提升技能使用频率，技能流核心性格，冲关打高分首选</t>
+  </si>
+  <si>
+    <t>char_002</t>
+  </si>
+  <si>
+    <t>话痨</t>
+  </si>
+  <si>
+    <t>每次释放主动技能，额外获得对局分数</t>
+  </si>
+  <si>
+    <t>放大技能释放收益，与傲娇形成完美技能流组合</t>
+  </si>
+  <si>
+    <t>经济收益类</t>
+  </si>
+  <si>
+    <t>char_003</t>
+  </si>
+  <si>
+    <t>吃货</t>
+  </si>
+  <si>
+    <t>额外鱼干百分比加成，随好感度从5%提升至30%</t>
+  </si>
+  <si>
+    <t>最通用的鱼干收益提升，适配所有上阵场景，养成核心性格</t>
+  </si>
+  <si>
+    <t>char_004</t>
+  </si>
+  <si>
+    <t>独行</t>
+  </si>
+  <si>
+    <t>单猫出战时，额外鱼干比例随好感度提升</t>
+  </si>
+  <si>
+    <t>适配单猫冲关、极限挑战场景，给单猫玩法专属收益激励</t>
+  </si>
+  <si>
+    <t>char_005</t>
+  </si>
+  <si>
+    <t>狡黠</t>
+  </si>
+  <si>
+    <t>提升本局额外鱼干上限，随好感度从默认2个最高提升至4个</t>
+  </si>
+  <si>
+    <t>突破鱼干收益天花板，和吃货形成叠加，高收益场景核心性格</t>
+  </si>
+  <si>
+    <t>生存容错类</t>
+  </si>
+  <si>
+    <t>char_006</t>
+  </si>
+  <si>
+    <t>胆小</t>
+  </si>
+  <si>
+    <t>干扰牌负面效果减免，高好感度下可完全免疫干扰牌效果</t>
+  </si>
+  <si>
+    <t>从源头减少关卡负面干扰，降低玩家操作压力，新手友好</t>
+  </si>
+  <si>
+    <t>char_007</t>
+  </si>
+  <si>
+    <t>黏人</t>
+  </si>
+  <si>
+    <t>关卡容错续命，从概率豁免失误，到固定豁免1次失误，再到额外免费续命1次</t>
+  </si>
+  <si>
+    <t>最核心的容错性格，直接给玩家提供失误缓冲，大幅降低关卡翻车概率</t>
+  </si>
+  <si>
+    <t>char_008</t>
+  </si>
+  <si>
+    <t>胆大</t>
+  </si>
+  <si>
+    <t>危险牌、操作失误的扣分与失败惩罚减免</t>
+  </si>
+  <si>
+    <t>减少失误带来的负面后果，和黏人形成互补，进一步提升关卡生存能力</t>
+  </si>
+  <si>
+    <t>得分体验类</t>
+  </si>
+  <si>
+    <t>char_009</t>
   </si>
   <si>
     <t>高冷</t>
   </si>
   <si>
-    <t>陌生</t>
-  </si>
-  <si>
-    <t>cat_002</t>
-  </si>
-  <si>
-    <t>布偶猫</t>
-  </si>
-  <si>
-    <t>R级（稀有）</t>
-  </si>
-  <si>
-    <t>基础鱼干收益+20%</t>
-  </si>
-  <si>
-    <t>黏人</t>
-  </si>
-  <si>
-    <t>cat_003</t>
-  </si>
-  <si>
-    <t>橘猫</t>
-  </si>
-  <si>
-    <t>吃货</t>
-  </si>
-  <si>
-    <t>cat_004</t>
-  </si>
-  <si>
-    <t>三花猫</t>
-  </si>
-  <si>
-    <t>SR级（超稀有）</t>
-  </si>
-  <si>
-    <t>蹦跶：随机跳走棋盘上2张干扰卡</t>
-  </si>
-  <si>
-    <t>基础鱼干收益+25%</t>
-  </si>
-  <si>
-    <t>胆小</t>
-  </si>
-  <si>
-    <t>cat_005</t>
-  </si>
-  <si>
-    <t>无毛猫</t>
-  </si>
-  <si>
-    <t>爪痕：自动移出棋盘上1张干扰卡</t>
-  </si>
-  <si>
-    <t>傲娇</t>
-  </si>
-  <si>
-    <t>cat_006</t>
-  </si>
-  <si>
-    <t>暹罗猫</t>
-  </si>
-  <si>
-    <t>胆大</t>
-  </si>
-  <si>
-    <t>cat_007</t>
-  </si>
-  <si>
-    <t>白猫</t>
-  </si>
-  <si>
-    <t>SSR级（典藏）</t>
-  </si>
-  <si>
-    <t>清浴：开局消除棋盘上所有干扰卡</t>
-  </si>
-  <si>
-    <t>基础鱼干收益+30%</t>
-  </si>
-  <si>
-    <t>洁癖</t>
-  </si>
-  <si>
-    <t>cat_008</t>
-  </si>
-  <si>
-    <t>黑猫</t>
-  </si>
-  <si>
-    <t>cat_009</t>
-  </si>
-  <si>
-    <t>奶牛猫</t>
-  </si>
-  <si>
-    <t>话痨</t>
-  </si>
-  <si>
-    <t>cat_010</t>
-  </si>
-  <si>
-    <t>曼基康猫</t>
+    <t>普通消除得分加成，随好感度从5%提升至30%</t>
+  </si>
+  <si>
+    <t>不影响鱼干收益，仅提升对局基础得分，适配打高分、冲排行榜场景</t>
+  </si>
+  <si>
+    <t>char_010</t>
   </si>
   <si>
     <t>懒散</t>
-  </si>
-  <si>
-    <t>cat_011</t>
-  </si>
-  <si>
-    <t>德文猫</t>
-  </si>
-  <si>
-    <t>独行</t>
-  </si>
-  <si>
-    <t>cat_012</t>
-  </si>
-  <si>
-    <t>幸运猫</t>
-  </si>
-  <si>
-    <t>基础鱼干收益+40%</t>
-  </si>
-  <si>
-    <t>狡黠</t>
-  </si>
-  <si>
-    <t>分类</t>
-  </si>
-  <si>
-    <t>性格ID</t>
-  </si>
-  <si>
-    <t>性格名称</t>
-  </si>
-  <si>
-    <t>核心效果</t>
-  </si>
-  <si>
-    <t>玩法说明</t>
-  </si>
-  <si>
-    <t>技能循环类</t>
-  </si>
-  <si>
-    <t>char_001</t>
-  </si>
-  <si>
-    <t>主动技能冷却缩减，高好感度下额外增加1次本局技能使用次数</t>
-  </si>
-  <si>
-    <t>提升技能使用频率，技能流核心性格，冲关打高分首选</t>
-  </si>
-  <si>
-    <t>char_002</t>
-  </si>
-  <si>
-    <t>每次释放主动技能，额外获得对局分数</t>
-  </si>
-  <si>
-    <t>放大技能释放收益，与傲娇形成完美技能流组合</t>
-  </si>
-  <si>
-    <t>经济收益类</t>
-  </si>
-  <si>
-    <t>char_003</t>
-  </si>
-  <si>
-    <t>额外鱼干百分比加成，随好感度从5%提升至30%</t>
-  </si>
-  <si>
-    <t>最通用的鱼干收益提升，适配所有上阵场景，养成核心性格</t>
-  </si>
-  <si>
-    <t>char_004</t>
-  </si>
-  <si>
-    <t>单猫出战时，额外鱼干比例随好感度提升</t>
-  </si>
-  <si>
-    <t>适配单猫冲关、极限挑战场景，给单猫玩法专属收益激励</t>
-  </si>
-  <si>
-    <t>char_005</t>
-  </si>
-  <si>
-    <t>提升本局额外鱼干上限，随好感度从默认2个最高提升至4个</t>
-  </si>
-  <si>
-    <t>突破鱼干收益天花板，和吃货形成叠加，高收益场景核心性格</t>
-  </si>
-  <si>
-    <t>生存容错类</t>
-  </si>
-  <si>
-    <t>char_006</t>
-  </si>
-  <si>
-    <t>干扰牌负面效果减免，高好感度下可完全免疫干扰牌效果</t>
-  </si>
-  <si>
-    <t>从源头减少关卡负面干扰，降低玩家操作压力，新手友好</t>
-  </si>
-  <si>
-    <t>char_007</t>
-  </si>
-  <si>
-    <t>关卡容错续命，从概率豁免失误，到固定豁免1次失误，再到额外免费续命1次</t>
-  </si>
-  <si>
-    <t>最核心的容错性格，直接给玩家提供失误缓冲，大幅降低关卡翻车概率</t>
-  </si>
-  <si>
-    <t>char_008</t>
-  </si>
-  <si>
-    <t>危险牌、操作失误的扣分与失败惩罚减免</t>
-  </si>
-  <si>
-    <t>减少失误带来的负面后果，和黏人形成互补，进一步提升关卡生存能力</t>
-  </si>
-  <si>
-    <t>得分体验类</t>
-  </si>
-  <si>
-    <t>char_009</t>
-  </si>
-  <si>
-    <t>普通消除得分加成，随好感度从5%提升至30%</t>
-  </si>
-  <si>
-    <t>不影响鱼干收益，仅提升对局基础得分，适配打高分、冲排行榜场景</t>
-  </si>
-  <si>
-    <t>char_010</t>
   </si>
   <si>
     <t>计时关卡限时延长，随好感度从+2秒提升至+8秒</t>
@@ -689,7 +818,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -713,6 +842,19 @@
     <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1198,28 +1340,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1228,122 +1361,131 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1360,6 +1502,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1683,18 +1837,20 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="15.2" outlineLevelCol="6"/>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="15.2"/>
   <cols>
     <col min="1" max="1" width="11.5384615384615" customWidth="1"/>
     <col min="2" max="2" width="14.2596153846154" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="18.4230769230769" customWidth="1"/>
-    <col min="6" max="7" width="7" customWidth="1"/>
+    <col min="3" max="3" width="19.7115384615385" customWidth="1"/>
+    <col min="4" max="4" width="13.6153846153846" customWidth="1"/>
+    <col min="5" max="5" width="38.1346153846154" customWidth="1"/>
+    <col min="6" max="6" width="11.375" customWidth="1"/>
+    <col min="7" max="7" width="45.0288461538462" customWidth="1"/>
+    <col min="8" max="8" width="22.1153846153846" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:7">
+    <row r="1" ht="36" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1716,284 +1872,413 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="36" customHeight="1" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:7">
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="1:7">
+    </row>
+    <row r="4" ht="36" customHeight="1" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:7">
+    </row>
+    <row r="5" ht="36" customHeight="1" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1" spans="1:7">
+        <v>30</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="1:7">
+        <v>36</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1" spans="1:7">
+        <v>43</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1" spans="1:7">
+      <c r="D8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1" spans="1:7">
+        <v>55</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1" spans="1:7">
+        <v>61</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1" spans="1:7">
+        <v>68</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:7">
+        <v>74</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" ht="18" spans="1:9">
+      <c r="A14" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="4:4">
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="4:4">
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="4:4">
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="4:4">
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="4:4">
+      <c r="D25" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B14:I14"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -2016,189 +2301,189 @@
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>18</v>
+        <v>122</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>91</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>93</v>
+        <v>136</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>94</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2218,129 +2503,129 @@
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="27.5576923076923" customWidth="1"/>
     <col min="3" max="3" width="37.0192307692308" customWidth="1"/>
-    <col min="4" max="4" width="26.5961538461538" customWidth="1"/>
+    <col min="4" max="4" width="34.6057692307692" customWidth="1"/>
     <col min="5" max="5" width="24.0384615384615" customWidth="1"/>
     <col min="6" max="6" width="33.1634615384615" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>99</v>
+        <v>142</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6">
       <c r="A2" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6">
       <c r="A3" s="5" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>108</v>
+        <v>151</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>113</v>
+        <v>156</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>124</v>
+        <v>167</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2364,134 +2649,134 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>128</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>131</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>133</v>
+        <v>176</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>137</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>140</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>143</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>145</v>
+        <v>188</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>147</v>
+        <v>190</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>149</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>155</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>156</v>
+        <v>199</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>161</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2518,142 +2803,142 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>163</v>
+        <v>206</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>166</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>167</v>
+        <v>210</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>168</v>
+        <v>211</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>169</v>
+        <v>212</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>171</v>
+        <v>214</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>176</v>
+        <v>219</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>178</v>
+        <v>221</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>180</v>
+        <v>223</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>181</v>
+        <v>224</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>183</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>184</v>
+        <v>227</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>186</v>
+        <v>229</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>181</v>
+        <v>224</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>187</v>
+        <v>230</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>188</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>189</v>
+        <v>232</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>190</v>
+        <v>233</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>192</v>
+        <v>235</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>193</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>194</v>
+        <v>237</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>195</v>
+        <v>238</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>196</v>
+        <v>239</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>181</v>
+        <v>224</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>197</v>
+        <v>240</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>198</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -2677,68 +2962,68 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>201</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" ht="104" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>203</v>
+        <v>246</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" ht="67" customHeight="1" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" ht="81" customHeight="1" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" ht="81" customHeight="1" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>211</v>
+        <v>254</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" ht="81" customHeight="1" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>212</v>
+        <v>255</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>213</v>
+        <v>256</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>214</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
